--- a/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Observations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE2EDC9-FC0D-4415-9052-79F5E1D9095A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8CA950-8B6A-448D-8E20-39F55F02C79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{459658F3-8D1E-4130-B424-C0B52D12950E}"/>
+    <workbookView xWindow="2775" yWindow="3780" windowWidth="21600" windowHeight="12645" xr2:uid="{459658F3-8D1E-4130-B424-C0B52D12950E}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="296">
   <si>
     <t>StepNo</t>
   </si>
@@ -921,6 +921,12 @@
   </si>
   <si>
     <t>Login password</t>
+  </si>
+  <si>
+    <t>Click Find record to open the patient search form</t>
+  </si>
+  <si>
+    <t>lnkTaskPanePatient</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A1CEEA3-A3D6-4EB3-A824-931AE508C77C}">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -1448,13 +1454,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>294</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>295</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1462,19 +1471,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1482,16 +1485,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1499,13 +1505,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
       </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1513,16 +1522,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1530,13 +1536,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1544,19 +1553,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
       <c r="F13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1564,19 +1567,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
       </c>
-      <c r="J14" t="s">
-        <v>32</v>
+      <c r="K14" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1584,19 +1587,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
       </c>
-      <c r="K15" t="s">
-        <v>47</v>
+      <c r="J15" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1604,16 +1607,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1621,13 +1627,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>40</v>
       </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1635,16 +1644,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1652,19 +1658,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1672,19 +1675,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="K20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1692,19 +1695,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="K21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1712,19 +1715,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
         <v>31</v>
       </c>
       <c r="K22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1732,19 +1735,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
       </c>
       <c r="K23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1752,16 +1755,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
         <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="K24" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1769,13 +1775,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1783,19 +1792,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
         <v>40</v>
       </c>
-      <c r="D26" t="s">
-        <v>72</v>
-      </c>
       <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="K26" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1803,19 +1806,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
         <v>57</v>
       </c>
       <c r="K27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1823,19 +1826,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>57</v>
       </c>
       <c r="K28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1843,19 +1846,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
         <v>57</v>
       </c>
       <c r="K29" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1863,19 +1866,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
         <v>57</v>
       </c>
       <c r="K30" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1883,19 +1886,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
         <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F31" t="s">
         <v>57</v>
       </c>
       <c r="K31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1903,16 +1906,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>57</v>
+      </c>
+      <c r="K32" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1920,13 +1926,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1934,19 +1943,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
         <v>92</v>
       </c>
-      <c r="D34" t="s">
-        <v>94</v>
-      </c>
       <c r="F34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1954,7 +1957,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
         <v>92</v>
@@ -1963,13 +1966,10 @@
         <v>94</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
-      </c>
-      <c r="G35" t="s">
-        <v>99</v>
-      </c>
-      <c r="H35" t="s">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="J35" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1977,16 +1977,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
         <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>98</v>
+      </c>
+      <c r="G36" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -1994,13 +2000,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>92</v>
+      </c>
+      <c r="D37" t="s">
+        <v>102</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2008,16 +2017,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="D38" t="s">
-        <v>105</v>
-      </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2025,13 +2031,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>105</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2039,19 +2048,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
         <v>29</v>
       </c>
-      <c r="D40" t="s">
-        <v>30</v>
-      </c>
       <c r="F40" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2059,16 +2062,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
         <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2076,13 +2082,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C42" t="s">
         <v>29</v>
       </c>
+      <c r="D42" t="s">
+        <v>34</v>
+      </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2090,16 +2099,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2107,13 +2113,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="D44" t="s">
+        <v>110</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2121,25 +2130,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
         <v>112</v>
       </c>
-      <c r="D45" t="s">
-        <v>114</v>
-      </c>
       <c r="F45" t="s">
-        <v>98</v>
-      </c>
-      <c r="G45" t="s">
-        <v>115</v>
-      </c>
-      <c r="H45" t="s">
-        <v>116</v>
-      </c>
-      <c r="J45" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2147,7 +2144,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
         <v>112</v>
@@ -2156,10 +2153,16 @@
         <v>114</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
-      </c>
-      <c r="J46" t="s">
-        <v>118</v>
+        <v>98</v>
+      </c>
+      <c r="G46" t="s">
+        <v>115</v>
+      </c>
+      <c r="H46" t="s">
+        <v>116</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2167,13 +2170,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
       </c>
       <c r="F47" t="s">
-        <v>120</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="J47" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2181,16 +2190,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
-      </c>
-      <c r="C48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2198,13 +2204,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
         <v>112</v>
       </c>
+      <c r="D49" t="s">
+        <v>122</v>
+      </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2212,16 +2221,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
         <v>112</v>
       </c>
-      <c r="D50" t="s">
-        <v>125</v>
-      </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2229,13 +2235,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>112</v>
+      </c>
+      <c r="D51" t="s">
+        <v>125</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2243,19 +2252,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
         <v>127</v>
       </c>
-      <c r="D52" t="s">
-        <v>129</v>
-      </c>
       <c r="F52" t="s">
-        <v>57</v>
-      </c>
-      <c r="K52" t="s">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2263,19 +2266,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s">
         <v>127</v>
       </c>
       <c r="D53" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F53" t="s">
         <v>57</v>
       </c>
       <c r="K53" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2283,19 +2286,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
         <v>127</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F54" t="s">
         <v>57</v>
       </c>
       <c r="K54" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2303,19 +2306,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C55" t="s">
         <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F55" t="s">
         <v>57</v>
       </c>
       <c r="K55" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2323,16 +2326,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
         <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>57</v>
+      </c>
+      <c r="K56" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2340,13 +2346,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="D57" t="s">
+        <v>141</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2354,25 +2363,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
-      </c>
-      <c r="D58" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="F58" t="s">
-        <v>98</v>
-      </c>
-      <c r="G58" t="s">
-        <v>115</v>
-      </c>
-      <c r="H58" t="s">
-        <v>116</v>
-      </c>
-      <c r="J58" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2380,12 +2377,24 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="C59" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" t="s">
+        <v>51</v>
       </c>
       <c r="F59" t="s">
-        <v>120</v>
-      </c>
-      <c r="J59">
+        <v>98</v>
+      </c>
+      <c r="G59" t="s">
+        <v>115</v>
+      </c>
+      <c r="H59" t="s">
+        <v>116</v>
+      </c>
+      <c r="J59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2394,16 +2403,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
-      </c>
-      <c r="C60" t="s">
-        <v>144</v>
-      </c>
-      <c r="D60" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2411,13 +2417,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
         <v>144</v>
       </c>
       <c r="D61" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -2428,13 +2434,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C62" t="s">
-        <v>150</v>
+        <v>144</v>
+      </c>
+      <c r="D62" t="s">
+        <v>148</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2442,19 +2451,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
         <v>150</v>
       </c>
-      <c r="D63" t="s">
-        <v>152</v>
-      </c>
       <c r="F63" t="s">
-        <v>57</v>
-      </c>
-      <c r="K63" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2462,19 +2465,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
         <v>150</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F64" t="s">
         <v>57</v>
       </c>
       <c r="K64" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2482,19 +2485,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C65" t="s">
         <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F65" t="s">
         <v>57</v>
       </c>
       <c r="K65" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2502,19 +2505,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
         <v>150</v>
       </c>
       <c r="D66" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F66" t="s">
         <v>57</v>
       </c>
       <c r="K66" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2522,16 +2525,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C67" t="s">
         <v>150</v>
       </c>
       <c r="D67" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>23</v>
+        <v>57</v>
+      </c>
+      <c r="K67" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2539,13 +2545,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>165</v>
+        <v>150</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2553,16 +2562,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C69" t="s">
         <v>165</v>
       </c>
-      <c r="D69" t="s">
-        <v>90</v>
-      </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2570,13 +2576,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>165</v>
+      </c>
+      <c r="D70" t="s">
+        <v>90</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2584,25 +2593,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" t="s">
         <v>112</v>
       </c>
-      <c r="D71" t="s">
-        <v>114</v>
-      </c>
       <c r="F71" t="s">
-        <v>98</v>
-      </c>
-      <c r="G71" t="s">
-        <v>115</v>
-      </c>
-      <c r="H71" t="s">
-        <v>116</v>
-      </c>
-      <c r="J71" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2610,12 +2607,24 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="C72" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" t="s">
+        <v>114</v>
       </c>
       <c r="F72" t="s">
-        <v>120</v>
-      </c>
-      <c r="J72">
+        <v>98</v>
+      </c>
+      <c r="G72" t="s">
+        <v>115</v>
+      </c>
+      <c r="H72" t="s">
+        <v>116</v>
+      </c>
+      <c r="J72" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2624,16 +2633,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
-      </c>
-      <c r="C73" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2641,13 +2647,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
+        <v>171</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2655,25 +2664,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
         <v>173</v>
       </c>
-      <c r="D75" t="s">
-        <v>175</v>
-      </c>
       <c r="F75" t="s">
-        <v>98</v>
-      </c>
-      <c r="G75" t="s">
-        <v>115</v>
-      </c>
-      <c r="H75" t="s">
-        <v>116</v>
-      </c>
-      <c r="J75" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2681,12 +2678,24 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="C76" t="s">
+        <v>173</v>
+      </c>
+      <c r="D76" t="s">
+        <v>175</v>
       </c>
       <c r="F76" t="s">
-        <v>120</v>
-      </c>
-      <c r="J76">
+        <v>98</v>
+      </c>
+      <c r="G76" t="s">
+        <v>115</v>
+      </c>
+      <c r="H76" t="s">
+        <v>116</v>
+      </c>
+      <c r="J76" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2695,16 +2704,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
-      </c>
-      <c r="C77" t="s">
-        <v>173</v>
-      </c>
-      <c r="D77" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -2712,13 +2718,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C78" t="s">
-        <v>179</v>
+        <v>173</v>
+      </c>
+      <c r="D78" t="s">
+        <v>175</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2726,19 +2735,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C79" t="s">
         <v>179</v>
       </c>
-      <c r="D79" t="s">
-        <v>181</v>
-      </c>
       <c r="F79" t="s">
-        <v>31</v>
-      </c>
-      <c r="K79" t="s">
-        <v>182</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2746,16 +2749,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C80" t="s">
         <v>179</v>
       </c>
       <c r="D80" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F80" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="K80" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2763,13 +2769,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C81" t="s">
         <v>179</v>
       </c>
+      <c r="D81" t="s">
+        <v>184</v>
+      </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2777,25 +2786,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
         <v>179</v>
       </c>
-      <c r="D82" t="s">
-        <v>187</v>
-      </c>
       <c r="F82" t="s">
-        <v>98</v>
-      </c>
-      <c r="G82" t="s">
-        <v>115</v>
-      </c>
-      <c r="H82" t="s">
-        <v>116</v>
-      </c>
-      <c r="J82" t="b">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2803,7 +2800,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C83" t="s">
         <v>179</v>
@@ -2812,7 +2809,16 @@
         <v>187</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>98</v>
+      </c>
+      <c r="G83" t="s">
+        <v>115</v>
+      </c>
+      <c r="H83" t="s">
+        <v>116</v>
+      </c>
+      <c r="J83" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2820,13 +2826,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C84" t="s">
         <v>179</v>
       </c>
+      <c r="D84" t="s">
+        <v>187</v>
+      </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2834,13 +2843,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>189</v>
+      </c>
+      <c r="C85" t="s">
+        <v>179</v>
       </c>
       <c r="F85" t="s">
-        <v>120</v>
-      </c>
-      <c r="J85">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2848,16 +2857,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
-      </c>
-      <c r="C86" t="s">
-        <v>179</v>
-      </c>
-      <c r="D86" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F86" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2865,13 +2871,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C87" t="s">
         <v>179</v>
       </c>
+      <c r="D87" t="s">
+        <v>192</v>
+      </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2879,16 +2888,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C88" t="s">
         <v>179</v>
       </c>
-      <c r="D88" t="s">
-        <v>195</v>
-      </c>
       <c r="F88" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2896,13 +2902,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C89" t="s">
         <v>179</v>
       </c>
+      <c r="D89" t="s">
+        <v>195</v>
+      </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2910,13 +2919,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>197</v>
+        <v>196</v>
+      </c>
+      <c r="C90" t="s">
+        <v>179</v>
       </c>
       <c r="F90" t="s">
-        <v>120</v>
-      </c>
-      <c r="J90">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2924,16 +2933,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>198</v>
-      </c>
-      <c r="C91" t="s">
-        <v>179</v>
-      </c>
-      <c r="D91" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F91" t="s">
-        <v>23</v>
+        <v>120</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -2941,13 +2947,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C92" t="s">
         <v>179</v>
       </c>
+      <c r="D92" t="s">
+        <v>199</v>
+      </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -2955,19 +2964,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C93" t="s">
         <v>179</v>
       </c>
-      <c r="D93" t="s">
-        <v>202</v>
-      </c>
       <c r="F93" t="s">
-        <v>31</v>
-      </c>
-      <c r="K93" t="s">
-        <v>203</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -2975,19 +2978,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C94" t="s">
         <v>179</v>
       </c>
       <c r="D94" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F94" t="s">
         <v>31</v>
       </c>
       <c r="K94" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -2995,19 +2998,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C95" t="s">
         <v>179</v>
       </c>
       <c r="D95" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F95" t="s">
         <v>31</v>
       </c>
       <c r="K95" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3015,127 +3018,121 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C96" t="s">
         <v>179</v>
       </c>
       <c r="D96" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F96" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="K96" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
         <v>179</v>
       </c>
       <c r="D97" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F97" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="K97" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C98" t="s">
         <v>179</v>
       </c>
+      <c r="D98" t="s">
+        <v>214</v>
+      </c>
       <c r="F98" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>215</v>
+      </c>
+      <c r="C99" t="s">
+        <v>179</v>
       </c>
       <c r="F99" t="s">
-        <v>120</v>
-      </c>
-      <c r="J99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>217</v>
-      </c>
-      <c r="C100" t="s">
-        <v>179</v>
-      </c>
-      <c r="D100" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F100" t="s">
-        <v>98</v>
-      </c>
-      <c r="G100" t="s">
-        <v>99</v>
-      </c>
-      <c r="H100" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C101" t="s">
         <v>179</v>
       </c>
       <c r="D101" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F101" t="s">
         <v>98</v>
       </c>
       <c r="G101" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="H101" t="s">
-        <v>116</v>
-      </c>
-      <c r="J101" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C102" t="s">
         <v>179</v>
       </c>
       <c r="D102" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F102" t="s">
         <v>98</v>
@@ -3150,65 +3147,91 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>221</v>
+        <v>220</v>
+      </c>
+      <c r="C103" t="s">
+        <v>179</v>
+      </c>
+      <c r="D103" t="s">
+        <v>205</v>
       </c>
       <c r="F103" t="s">
-        <v>120</v>
-      </c>
-      <c r="J103">
+        <v>98</v>
+      </c>
+      <c r="G103" t="s">
+        <v>115</v>
+      </c>
+      <c r="H103" t="s">
+        <v>116</v>
+      </c>
+      <c r="J103" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>222</v>
-      </c>
-      <c r="C104" t="s">
-        <v>19</v>
-      </c>
-      <c r="D104" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F104" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C105" t="s">
         <v>19</v>
       </c>
       <c r="D105" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F105" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>224</v>
+      </c>
+      <c r="C106" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
         <v>226</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C107" t="s">
         <v>15</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F107" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3668,4 +3691,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Observations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8CA950-8B6A-448D-8E20-39F55F02C79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B1E702-A9A7-4FB9-B45B-1C76DED79B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="3780" windowWidth="21600" windowHeight="12645" xr2:uid="{459658F3-8D1E-4130-B424-C0B52D12950E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{459658F3-8D1E-4130-B424-C0B52D12950E}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="297">
   <si>
     <t>StepNo</t>
   </si>
@@ -927,6 +927,9 @@
   </si>
   <si>
     <t>lnkTaskPanePatient</t>
+  </si>
+  <si>
+    <t>pageSearchPatient</t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1511,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>296</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Observations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B1E702-A9A7-4FB9-B45B-1C76DED79B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AE98C1-383F-4635-9E2B-32A98FAF7CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{459658F3-8D1E-4130-B424-C0B52D12950E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="296">
   <si>
     <t>StepNo</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>launchUrl</t>
-  </si>
-  <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
   </si>
   <si>
     <t>Login with valid credentials</t>
@@ -1386,25 +1383,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1412,13 +1406,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1426,16 +1420,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1443,13 +1437,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1457,16 +1451,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>294</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>295</v>
-      </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1474,13 +1468,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>26</v>
-      </c>
-      <c r="J8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1488,19 +1482,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
+      <c r="J9" t="s">
         <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1508,16 +1502,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1525,13 +1519,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1539,16 +1533,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1556,13 +1550,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1570,19 +1564,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1590,19 +1584,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
         <v>30</v>
       </c>
-      <c r="F15" t="s">
+      <c r="J15" t="s">
         <v>31</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1610,19 +1604,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1630,16 +1624,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1647,13 +1641,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1661,16 +1655,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
         <v>50</v>
       </c>
-      <c r="C19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>51</v>
-      </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1678,19 +1672,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
         <v>52</v>
       </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" t="s">
         <v>53</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1698,19 +1692,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
         <v>55</v>
       </c>
-      <c r="C21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>56</v>
       </c>
-      <c r="F21" t="s">
+      <c r="K21" t="s">
         <v>57</v>
-      </c>
-      <c r="K21" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1718,19 +1712,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
         <v>59</v>
       </c>
-      <c r="C22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" t="s">
         <v>60</v>
-      </c>
-      <c r="F22" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1738,19 +1732,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
         <v>62</v>
       </c>
-      <c r="C23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" t="s">
         <v>63</v>
-      </c>
-      <c r="F23" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1758,19 +1752,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
         <v>65</v>
       </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" t="s">
         <v>66</v>
-      </c>
-      <c r="F24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1778,16 +1772,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
         <v>68</v>
       </c>
-      <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" t="s">
-        <v>69</v>
-      </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1795,13 +1789,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1809,19 +1803,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
         <v>71</v>
       </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" t="s">
         <v>72</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="K27" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1829,19 +1823,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
         <v>74</v>
       </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-      <c r="K28" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1849,19 +1843,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
         <v>77</v>
       </c>
-      <c r="C29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" t="s">
         <v>78</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="K29" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1869,19 +1863,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
         <v>80</v>
       </c>
-      <c r="C30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" t="s">
         <v>81</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="K30" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1889,19 +1883,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
         <v>83</v>
       </c>
-      <c r="C31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" t="s">
         <v>84</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-      <c r="K31" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1909,19 +1903,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" t="s">
         <v>86</v>
       </c>
-      <c r="C32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" t="s">
         <v>87</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-      <c r="K32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1929,16 +1923,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
         <v>89</v>
       </c>
-      <c r="C33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" t="s">
-        <v>90</v>
-      </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1946,13 +1940,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" t="s">
         <v>91</v>
       </c>
-      <c r="C34" t="s">
-        <v>92</v>
-      </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1960,19 +1954,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" t="s">
         <v>93</v>
       </c>
-      <c r="C35" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>94</v>
       </c>
-      <c r="F35" t="s">
+      <c r="J35" t="s">
         <v>95</v>
-      </c>
-      <c r="J35" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1980,22 +1974,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" t="s">
         <v>97</v>
       </c>
-      <c r="C36" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>98</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>99</v>
-      </c>
-      <c r="H36" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2003,16 +1997,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" t="s">
         <v>101</v>
       </c>
-      <c r="C37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>102</v>
-      </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2020,13 +2014,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
         <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2034,16 +2028,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
         <v>104</v>
       </c>
-      <c r="C39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" t="s">
-        <v>105</v>
-      </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2051,13 +2045,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2065,19 +2059,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
         <v>29</v>
       </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
         <v>30</v>
       </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
         <v>31</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2085,16 +2079,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" t="s">
         <v>33</v>
       </c>
-      <c r="C42" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" t="s">
-        <v>34</v>
-      </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2102,13 +2096,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2116,16 +2110,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
         <v>108</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>109</v>
       </c>
-      <c r="D44" t="s">
-        <v>110</v>
-      </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2133,13 +2127,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" t="s">
         <v>111</v>
       </c>
-      <c r="C45" t="s">
-        <v>112</v>
-      </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2147,22 +2141,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" t="s">
         <v>113</v>
       </c>
-      <c r="C46" t="s">
-        <v>112</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
+        <v>97</v>
+      </c>
+      <c r="G46" t="s">
         <v>114</v>
       </c>
-      <c r="F46" t="s">
-        <v>98</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>115</v>
-      </c>
-      <c r="H46" t="s">
-        <v>116</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -2173,19 +2167,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" t="s">
+        <v>94</v>
+      </c>
+      <c r="J47" t="s">
         <v>117</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" t="s">
-        <v>114</v>
-      </c>
-      <c r="F47" t="s">
-        <v>95</v>
-      </c>
-      <c r="J47" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2193,10 +2187,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>118</v>
+      </c>
+      <c r="F48" t="s">
         <v>119</v>
-      </c>
-      <c r="F48" t="s">
-        <v>120</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2207,16 +2201,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" t="s">
         <v>121</v>
       </c>
-      <c r="C49" t="s">
-        <v>112</v>
-      </c>
-      <c r="D49" t="s">
-        <v>122</v>
-      </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2224,13 +2218,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2238,16 +2232,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" t="s">
         <v>124</v>
       </c>
-      <c r="C51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2255,13 +2249,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" t="s">
         <v>126</v>
       </c>
-      <c r="C52" t="s">
-        <v>127</v>
-      </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2269,19 +2263,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
         <v>128</v>
       </c>
-      <c r="C53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>56</v>
+      </c>
+      <c r="K53" t="s">
         <v>129</v>
-      </c>
-      <c r="F53" t="s">
-        <v>57</v>
-      </c>
-      <c r="K53" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2289,19 +2283,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>130</v>
+      </c>
+      <c r="C54" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" t="s">
         <v>131</v>
       </c>
-      <c r="C54" t="s">
-        <v>127</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
+        <v>56</v>
+      </c>
+      <c r="K54" t="s">
         <v>132</v>
-      </c>
-      <c r="F54" t="s">
-        <v>57</v>
-      </c>
-      <c r="K54" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2309,19 +2303,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" t="s">
         <v>134</v>
       </c>
-      <c r="C55" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
+        <v>56</v>
+      </c>
+      <c r="K55" t="s">
         <v>135</v>
-      </c>
-      <c r="F55" t="s">
-        <v>57</v>
-      </c>
-      <c r="K55" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2329,19 +2323,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" t="s">
         <v>137</v>
       </c>
-      <c r="C56" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
+        <v>56</v>
+      </c>
+      <c r="K56" t="s">
         <v>138</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
-      <c r="K56" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2349,16 +2343,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" t="s">
         <v>140</v>
       </c>
-      <c r="C57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" t="s">
-        <v>141</v>
-      </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2366,13 +2360,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2380,22 +2374,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
         <v>143</v>
       </c>
-      <c r="C59" t="s">
-        <v>144</v>
-      </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G59" t="s">
+        <v>114</v>
+      </c>
+      <c r="H59" t="s">
         <v>115</v>
-      </c>
-      <c r="H59" t="s">
-        <v>116</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
@@ -2406,10 +2400,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2420,16 +2414,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2437,16 +2431,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62" t="s">
         <v>147</v>
       </c>
-      <c r="C62" t="s">
-        <v>144</v>
-      </c>
-      <c r="D62" t="s">
-        <v>148</v>
-      </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2454,13 +2448,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" t="s">
         <v>149</v>
       </c>
-      <c r="C63" t="s">
-        <v>150</v>
-      </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2468,19 +2462,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" t="s">
         <v>151</v>
       </c>
-      <c r="C64" t="s">
-        <v>150</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="F64" t="s">
+        <v>56</v>
+      </c>
+      <c r="K64" t="s">
         <v>152</v>
-      </c>
-      <c r="F64" t="s">
-        <v>57</v>
-      </c>
-      <c r="K64" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2488,19 +2482,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D65" t="s">
         <v>154</v>
       </c>
-      <c r="C65" t="s">
-        <v>150</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>56</v>
+      </c>
+      <c r="K65" t="s">
         <v>155</v>
-      </c>
-      <c r="F65" t="s">
-        <v>57</v>
-      </c>
-      <c r="K65" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2508,19 +2502,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66" t="s">
         <v>157</v>
       </c>
-      <c r="C66" t="s">
-        <v>150</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="F66" t="s">
+        <v>56</v>
+      </c>
+      <c r="K66" t="s">
         <v>158</v>
-      </c>
-      <c r="F66" t="s">
-        <v>57</v>
-      </c>
-      <c r="K66" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2528,19 +2522,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" t="s">
         <v>160</v>
       </c>
-      <c r="C67" t="s">
-        <v>150</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="F67" t="s">
+        <v>56</v>
+      </c>
+      <c r="K67" t="s">
         <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>57</v>
-      </c>
-      <c r="K67" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2548,16 +2542,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2565,13 +2559,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>163</v>
+      </c>
+      <c r="C69" t="s">
         <v>164</v>
       </c>
-      <c r="C69" t="s">
-        <v>165</v>
-      </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2579,16 +2573,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D70" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2596,13 +2590,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2610,22 +2604,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
+        <v>113</v>
+      </c>
+      <c r="F72" t="s">
+        <v>97</v>
+      </c>
+      <c r="G72" t="s">
         <v>114</v>
       </c>
-      <c r="F72" t="s">
-        <v>98</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>115</v>
-      </c>
-      <c r="H72" t="s">
-        <v>116</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
@@ -2636,10 +2630,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F73" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -2650,16 +2644,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" t="s">
+        <v>111</v>
+      </c>
+      <c r="D74" t="s">
         <v>170</v>
       </c>
-      <c r="C74" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" t="s">
-        <v>171</v>
-      </c>
       <c r="F74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2667,13 +2661,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>171</v>
+      </c>
+      <c r="C75" t="s">
         <v>172</v>
       </c>
-      <c r="C75" t="s">
-        <v>173</v>
-      </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2681,22 +2675,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" t="s">
+        <v>172</v>
+      </c>
+      <c r="D76" t="s">
         <v>174</v>
       </c>
-      <c r="C76" t="s">
-        <v>173</v>
-      </c>
-      <c r="D76" t="s">
-        <v>175</v>
-      </c>
       <c r="F76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G76" t="s">
+        <v>114</v>
+      </c>
+      <c r="H76" t="s">
         <v>115</v>
-      </c>
-      <c r="H76" t="s">
-        <v>116</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
@@ -2707,10 +2701,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -2721,16 +2715,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2738,13 +2732,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>177</v>
+      </c>
+      <c r="C79" t="s">
         <v>178</v>
       </c>
-      <c r="C79" t="s">
-        <v>179</v>
-      </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2752,19 +2746,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" t="s">
+        <v>178</v>
+      </c>
+      <c r="D80" t="s">
         <v>180</v>
       </c>
-      <c r="C80" t="s">
-        <v>179</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="F80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80" t="s">
         <v>181</v>
-      </c>
-      <c r="F80" t="s">
-        <v>31</v>
-      </c>
-      <c r="K80" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2772,16 +2766,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" t="s">
+        <v>178</v>
+      </c>
+      <c r="D81" t="s">
         <v>183</v>
       </c>
-      <c r="C81" t="s">
-        <v>179</v>
-      </c>
-      <c r="D81" t="s">
-        <v>184</v>
-      </c>
       <c r="F81" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2789,13 +2783,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C82" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2803,22 +2797,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" t="s">
+        <v>178</v>
+      </c>
+      <c r="D83" t="s">
         <v>186</v>
       </c>
-      <c r="C83" t="s">
-        <v>179</v>
-      </c>
-      <c r="D83" t="s">
-        <v>187</v>
-      </c>
       <c r="F83" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G83" t="s">
+        <v>114</v>
+      </c>
+      <c r="H83" t="s">
         <v>115</v>
-      </c>
-      <c r="H83" t="s">
-        <v>116</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -2829,16 +2823,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D84" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F84" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2846,13 +2840,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2860,10 +2854,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F86" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -2874,16 +2868,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" t="s">
+        <v>178</v>
+      </c>
+      <c r="D87" t="s">
         <v>191</v>
       </c>
-      <c r="C87" t="s">
-        <v>179</v>
-      </c>
-      <c r="D87" t="s">
-        <v>192</v>
-      </c>
       <c r="F87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2891,13 +2885,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C88" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2905,16 +2899,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>193</v>
+      </c>
+      <c r="C89" t="s">
+        <v>178</v>
+      </c>
+      <c r="D89" t="s">
         <v>194</v>
       </c>
-      <c r="C89" t="s">
-        <v>179</v>
-      </c>
-      <c r="D89" t="s">
-        <v>195</v>
-      </c>
       <c r="F89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2922,13 +2916,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2936,10 +2930,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -2950,16 +2944,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>197</v>
+      </c>
+      <c r="C92" t="s">
+        <v>178</v>
+      </c>
+      <c r="D92" t="s">
         <v>198</v>
       </c>
-      <c r="C92" t="s">
-        <v>179</v>
-      </c>
-      <c r="D92" t="s">
-        <v>199</v>
-      </c>
       <c r="F92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -2967,13 +2961,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C93" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -2981,19 +2975,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" t="s">
+        <v>178</v>
+      </c>
+      <c r="D94" t="s">
         <v>201</v>
       </c>
-      <c r="C94" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
+        <v>30</v>
+      </c>
+      <c r="K94" t="s">
         <v>202</v>
-      </c>
-      <c r="F94" t="s">
-        <v>31</v>
-      </c>
-      <c r="K94" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -3001,19 +2995,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>203</v>
+      </c>
+      <c r="C95" t="s">
+        <v>178</v>
+      </c>
+      <c r="D95" t="s">
         <v>204</v>
       </c>
-      <c r="C95" t="s">
-        <v>179</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="F95" t="s">
+        <v>30</v>
+      </c>
+      <c r="K95" t="s">
         <v>205</v>
-      </c>
-      <c r="F95" t="s">
-        <v>31</v>
-      </c>
-      <c r="K95" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3021,19 +3015,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>206</v>
+      </c>
+      <c r="C96" t="s">
+        <v>178</v>
+      </c>
+      <c r="D96" t="s">
         <v>207</v>
       </c>
-      <c r="C96" t="s">
-        <v>179</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96" t="s">
         <v>208</v>
-      </c>
-      <c r="F96" t="s">
-        <v>31</v>
-      </c>
-      <c r="K96" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -3041,19 +3035,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>209</v>
+      </c>
+      <c r="C97" t="s">
+        <v>178</v>
+      </c>
+      <c r="D97" t="s">
         <v>210</v>
       </c>
-      <c r="C97" t="s">
-        <v>179</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
+        <v>56</v>
+      </c>
+      <c r="K97" t="s">
         <v>211</v>
-      </c>
-      <c r="F97" t="s">
-        <v>57</v>
-      </c>
-      <c r="K97" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -3061,16 +3055,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98" t="s">
+        <v>178</v>
+      </c>
+      <c r="D98" t="s">
         <v>213</v>
       </c>
-      <c r="C98" t="s">
-        <v>179</v>
-      </c>
-      <c r="D98" t="s">
-        <v>214</v>
-      </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -3078,13 +3072,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -3092,10 +3086,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -3106,22 +3100,22 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>216</v>
+      </c>
+      <c r="C101" t="s">
+        <v>178</v>
+      </c>
+      <c r="D101" t="s">
         <v>217</v>
       </c>
-      <c r="C101" t="s">
-        <v>179</v>
-      </c>
-      <c r="D101" t="s">
-        <v>218</v>
-      </c>
       <c r="F101" t="s">
+        <v>97</v>
+      </c>
+      <c r="G101" t="s">
         <v>98</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>99</v>
-      </c>
-      <c r="H101" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3129,22 +3123,22 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C102" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F102" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G102" t="s">
+        <v>114</v>
+      </c>
+      <c r="H102" t="s">
         <v>115</v>
-      </c>
-      <c r="H102" t="s">
-        <v>116</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
@@ -3155,22 +3149,22 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C103" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D103" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G103" t="s">
+        <v>114</v>
+      </c>
+      <c r="H103" t="s">
         <v>115</v>
-      </c>
-      <c r="H103" t="s">
-        <v>116</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
@@ -3181,10 +3175,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F104" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -3195,16 +3189,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>221</v>
+      </c>
+      <c r="C105" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" t="s">
         <v>222</v>
       </c>
-      <c r="C105" t="s">
-        <v>19</v>
-      </c>
-      <c r="D105" t="s">
-        <v>223</v>
-      </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -3212,16 +3206,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>223</v>
+      </c>
+      <c r="C106" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" t="s">
         <v>224</v>
       </c>
-      <c r="C106" t="s">
-        <v>19</v>
-      </c>
-      <c r="D106" t="s">
-        <v>225</v>
-      </c>
       <c r="F106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -3229,13 +3223,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3278,96 +3272,96 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" t="s">
         <v>227</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>228</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>229</v>
-      </c>
-      <c r="D2" t="s">
-        <v>230</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -3376,52 +3370,52 @@
         <v>7890123456</v>
       </c>
       <c r="G2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H2" t="s">
         <v>231</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J2" t="s">
         <v>232</v>
       </c>
-      <c r="I2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>233</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>234</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>235</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>236</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>237</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>238</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>239</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>240</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>241</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>242</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>243</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>244</v>
-      </c>
-      <c r="V2" t="s">
-        <v>245</v>
       </c>
       <c r="W2">
         <v>98</v>
@@ -3430,10 +3424,10 @@
         <v>120</v>
       </c>
       <c r="Y2" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z2" t="s">
         <v>246</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3452,71 +3446,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3">
         <v>105</v>
@@ -3524,7 +3518,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -3532,7 +3526,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B11" s="3">
         <v>53</v>
@@ -3540,15 +3534,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -3556,7 +3550,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -3564,31 +3558,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>274</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B18" s="3">
         <v>9</v>
@@ -3596,18 +3590,18 @@
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3627,68 +3621,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" t="s">
         <v>284</v>
-      </c>
-      <c r="C2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3" t="s">
         <v>286</v>
-      </c>
-      <c r="C3" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" t="s">
         <v>289</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>290</v>
-      </c>
-      <c r="C5" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6" t="s">
         <v>292</v>
       </c>
-      <c r="B6" t="s">
-        <v>293</v>
-      </c>
       <c r="C6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Observations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AE98C1-383F-4635-9E2B-32A98FAF7CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65431574-2683-4E23-82FB-80F851700753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{459658F3-8D1E-4130-B424-C0B52D12950E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="297">
   <si>
     <t>StepNo</t>
   </si>
@@ -927,6 +927,9 @@
   </si>
   <si>
     <t>pageSearchPatient</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1545,7 @@
         <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1932,7 +1935,7 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2006,7 +2009,7 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Observations/LSTP_Observations_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Observations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65431574-2683-4E23-82FB-80F851700753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF8E451-12B7-4EC7-9CBF-F0A82B1F8D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{459658F3-8D1E-4130-B424-C0B52D12950E}"/>
   </bookViews>
@@ -218,27 +218,18 @@
     <t>Enter Home Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneHome</t>
-  </si>
-  <si>
     <t>TELEPHONEHOME</t>
   </si>
   <si>
     <t>Enter Mobile Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneMobile</t>
-  </si>
-  <si>
     <t>TELEPHONEMOBILE</t>
   </si>
   <si>
     <t>Enter Email address</t>
   </si>
   <si>
-    <t>txt_ TelephoneEmail</t>
-  </si>
-  <si>
     <t>EMAIL</t>
   </si>
   <si>
@@ -512,9 +503,6 @@
     <t>Select Intended Management</t>
   </si>
   <si>
-    <t>cmb_intended management</t>
-  </si>
-  <si>
     <t>INTENDED_MANAGEMENT</t>
   </si>
   <si>
@@ -930,6 +918,18 @@
   </si>
   <si>
     <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>txt_TelephoneHome</t>
+  </si>
+  <si>
+    <t>txt_TelephoneMobile</t>
+  </si>
+  <si>
+    <t>txt_TelephoneEmail</t>
+  </si>
+  <si>
+    <t>cmb_intendedManagement</t>
   </si>
 </sst>
 </file>
@@ -1454,13 +1454,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -1508,7 +1508,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1545,7 +1545,7 @@
         <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1721,13 +1721,13 @@
         <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>293</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,19 +1735,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
         <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1755,19 +1755,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>295</v>
       </c>
       <c r="F24" t="s">
         <v>30</v>
       </c>
       <c r="K24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1775,13 +1775,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
@@ -1792,7 +1792,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
         <v>39</v>
@@ -1806,19 +1806,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
         <v>56</v>
       </c>
       <c r="K27" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1826,19 +1826,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F28" t="s">
         <v>56</v>
       </c>
       <c r="K28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1846,19 +1846,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
         <v>56</v>
       </c>
       <c r="K29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1866,19 +1866,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
         <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s">
         <v>56</v>
       </c>
       <c r="K30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1886,19 +1886,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
         <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
         <v>56</v>
       </c>
       <c r="K31" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1906,19 +1906,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s">
         <v>56</v>
       </c>
       <c r="K32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1926,16 +1926,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1943,10 +1943,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -1957,19 +1957,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J35" t="s">
         <v>92</v>
-      </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" t="s">
-        <v>93</v>
-      </c>
-      <c r="F35" t="s">
-        <v>94</v>
-      </c>
-      <c r="J35" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1977,22 +1977,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" t="s">
         <v>96</v>
-      </c>
-      <c r="C36" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" t="s">
-        <v>93</v>
-      </c>
-      <c r="F36" t="s">
-        <v>97</v>
-      </c>
-      <c r="G36" t="s">
-        <v>98</v>
-      </c>
-      <c r="H36" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2000,16 +2000,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F37" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2017,7 +2017,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
@@ -2031,13 +2031,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>22</v>
@@ -2048,7 +2048,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
@@ -2062,7 +2062,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
@@ -2113,13 +2113,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F44" t="s">
         <v>22</v>
@@ -2130,10 +2130,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F45" t="s">
         <v>19</v>
@@ -2144,22 +2144,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" t="s">
+        <v>110</v>
+      </c>
+      <c r="F46" t="s">
+        <v>94</v>
+      </c>
+      <c r="G46" t="s">
+        <v>111</v>
+      </c>
+      <c r="H46" t="s">
         <v>112</v>
-      </c>
-      <c r="C46" t="s">
-        <v>111</v>
-      </c>
-      <c r="D46" t="s">
-        <v>113</v>
-      </c>
-      <c r="F46" t="s">
-        <v>97</v>
-      </c>
-      <c r="G46" t="s">
-        <v>114</v>
-      </c>
-      <c r="H46" t="s">
-        <v>115</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -2170,19 +2170,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D47" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F47" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J47" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2190,10 +2190,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F48" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2204,13 +2204,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
@@ -2221,10 +2221,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F50" t="s">
         <v>19</v>
@@ -2235,13 +2235,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
@@ -2252,10 +2252,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F52" t="s">
         <v>19</v>
@@ -2266,19 +2266,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F53" t="s">
         <v>56</v>
       </c>
       <c r="K53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2286,19 +2286,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D54" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F54" t="s">
         <v>56</v>
       </c>
       <c r="K54" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2306,19 +2306,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F55" t="s">
         <v>56</v>
       </c>
       <c r="K55" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2326,19 +2326,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D56" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F56" t="s">
         <v>56</v>
       </c>
       <c r="K56" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2346,13 +2346,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D57" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F57" t="s">
         <v>22</v>
@@ -2363,10 +2363,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C58" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F58" t="s">
         <v>19</v>
@@ -2377,22 +2377,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C59" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D59" t="s">
         <v>50</v>
       </c>
       <c r="F59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H59" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
@@ -2403,10 +2403,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2417,10 +2417,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C61" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D61" t="s">
         <v>50</v>
@@ -2434,13 +2434,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C62" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F62" t="s">
         <v>22</v>
@@ -2451,10 +2451,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C63" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F63" t="s">
         <v>19</v>
@@ -2465,19 +2465,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F64" t="s">
         <v>56</v>
       </c>
       <c r="K64" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2485,19 +2485,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F65" t="s">
         <v>56</v>
       </c>
       <c r="K65" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2505,19 +2505,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
-        <v>157</v>
+        <v>296</v>
       </c>
       <c r="F66" t="s">
         <v>56</v>
       </c>
       <c r="K66" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2525,19 +2525,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F67" t="s">
         <v>56</v>
       </c>
       <c r="K67" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2545,13 +2545,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F68" t="s">
         <v>22</v>
@@ -2562,10 +2562,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -2576,13 +2576,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D70" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F70" t="s">
         <v>22</v>
@@ -2593,10 +2593,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C71" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F71" t="s">
         <v>19</v>
@@ -2607,22 +2607,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C72" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" t="s">
+        <v>110</v>
+      </c>
+      <c r="F72" t="s">
+        <v>94</v>
+      </c>
+      <c r="G72" t="s">
         <v>111</v>
       </c>
-      <c r="D72" t="s">
-        <v>113</v>
-      </c>
-      <c r="F72" t="s">
-        <v>97</v>
-      </c>
-      <c r="G72" t="s">
-        <v>114</v>
-      </c>
       <c r="H72" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
@@ -2633,10 +2633,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F73" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -2647,13 +2647,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D74" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F74" t="s">
         <v>22</v>
@@ -2664,10 +2664,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F75" t="s">
         <v>19</v>
@@ -2678,22 +2678,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D76" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F76" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G76" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H76" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
@@ -2704,10 +2704,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F77" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -2718,13 +2718,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C78" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D78" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F78" t="s">
         <v>22</v>
@@ -2735,10 +2735,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>19</v>
@@ -2749,19 +2749,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C80" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D80" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F80" t="s">
         <v>30</v>
       </c>
       <c r="K80" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2769,13 +2769,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D81" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F81" t="s">
         <v>22</v>
@@ -2786,10 +2786,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C82" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
@@ -2800,22 +2800,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C83" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D83" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G83" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H83" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -2826,13 +2826,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C84" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D84" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F84" t="s">
         <v>22</v>
@@ -2843,10 +2843,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C85" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F85" t="s">
         <v>19</v>
@@ -2857,10 +2857,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F86" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -2871,13 +2871,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D87" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F87" t="s">
         <v>22</v>
@@ -2888,10 +2888,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F88" t="s">
         <v>19</v>
@@ -2902,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C89" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D89" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F89" t="s">
         <v>22</v>
@@ -2919,10 +2919,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C90" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2933,10 +2933,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F91" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -2947,13 +2947,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C92" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D92" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F92" t="s">
         <v>22</v>
@@ -2964,10 +2964,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C93" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -2978,19 +2978,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C94" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D94" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F94" t="s">
         <v>30</v>
       </c>
       <c r="K94" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -2998,19 +2998,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C95" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D95" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F95" t="s">
         <v>30</v>
       </c>
       <c r="K95" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3018,19 +3018,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C96" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D96" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F96" t="s">
         <v>30</v>
       </c>
       <c r="K96" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -3038,19 +3038,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C97" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D97" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
         <v>56</v>
       </c>
       <c r="K97" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -3058,13 +3058,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C98" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D98" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F98" t="s">
         <v>22</v>
@@ -3075,10 +3075,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C99" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -3089,10 +3089,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -3103,22 +3103,22 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C101" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D101" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F101" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G101" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H101" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3126,22 +3126,22 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C102" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D102" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F102" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G102" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H102" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
@@ -3152,22 +3152,22 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C103" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D103" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F103" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G103" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H103" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
@@ -3178,10 +3178,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F104" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -3192,13 +3192,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C105" t="s">
         <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F105" t="s">
         <v>22</v>
@@ -3209,13 +3209,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F106" t="s">
         <v>22</v>
@@ -3226,7 +3226,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -3287,84 +3287,84 @@
         <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -3373,52 +3373,52 @@
         <v>7890123456</v>
       </c>
       <c r="G2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L2" t="s">
         <v>230</v>
       </c>
-      <c r="H2" t="s">
+      <c r="M2" t="s">
         <v>231</v>
       </c>
-      <c r="I2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>232</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>233</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>234</v>
       </c>
-      <c r="M2" t="s">
+      <c r="Q2" t="s">
         <v>235</v>
       </c>
-      <c r="N2" t="s">
+      <c r="R2" t="s">
         <v>236</v>
       </c>
-      <c r="O2" t="s">
+      <c r="S2" t="s">
         <v>237</v>
       </c>
-      <c r="P2" t="s">
+      <c r="T2" t="s">
         <v>238</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="U2" t="s">
         <v>239</v>
       </c>
-      <c r="R2" t="s">
+      <c r="V2" t="s">
         <v>240</v>
-      </c>
-      <c r="S2" t="s">
-        <v>241</v>
-      </c>
-      <c r="T2" t="s">
-        <v>242</v>
-      </c>
-      <c r="U2" t="s">
-        <v>243</v>
-      </c>
-      <c r="V2" t="s">
-        <v>244</v>
       </c>
       <c r="W2">
         <v>98</v>
@@ -3427,10 +3427,10 @@
         <v>120</v>
       </c>
       <c r="Y2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3449,71 +3449,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B9" s="3">
         <v>105</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B11" s="3">
         <v>53</v>
@@ -3537,15 +3537,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -3561,31 +3561,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B18" s="3">
         <v>9</v>
@@ -3593,18 +3593,18 @@
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3624,13 +3624,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3638,54 +3638,54 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
